--- a/completed/dimerization_10.1021.acscatal.5b02001.xlsx
+++ b/completed/dimerization_10.1021.acscatal.5b02001.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/incomplete/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/completed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504228B-175C-5E45-A7B3-801020E84AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E775CA04-C0D2-784F-A28E-4D9D5C87095E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11900" yWindow="500" windowWidth="23940" windowHeight="15360" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="62">
   <si>
     <t>REACTION</t>
   </si>
@@ -83,9 +83,6 @@
     <t>DOI</t>
   </si>
   <si>
-    <t>Frequency (Hz)</t>
-  </si>
-  <si>
     <t>Ball Mill</t>
   </si>
   <si>
@@ -224,7 +221,7 @@
     <t>CC(C1=CC=C(C#C/C=C/C2=CC=C(C(C)(C)C)C=C2)C=C1)(C)C</t>
   </si>
   <si>
-    <t>Duration (hours)</t>
+    <t>Duration (hour)</t>
   </si>
 </sst>
 </file>
@@ -812,34 +809,34 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
         <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
       <c r="B5" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="17" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>21</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -918,11 +915,8 @@
       <c r="L8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="M8" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>62</v>
+      <c r="M8" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -938,598 +932,596 @@
       <c r="H9" s="10"/>
       <c r="I9" s="11"/>
       <c r="L9" s="10"/>
-      <c r="M9"/>
-      <c r="N9" s="11"/>
+      <c r="M9" s="11"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10">
+        <v>2.1</v>
+      </c>
+      <c r="H10" t="s">
         <v>40</v>
-      </c>
-      <c r="E10">
-        <v>2.1</v>
-      </c>
-      <c r="H10" t="s">
-        <v>41</v>
       </c>
       <c r="I10">
         <v>74</v>
       </c>
       <c r="J10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>16</v>
-      </c>
-      <c r="N10">
+        <v>15</v>
+      </c>
+      <c r="M10">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11">
         <v>2.1</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I11">
         <v>71</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>16</v>
-      </c>
-      <c r="N11">
+        <v>15</v>
+      </c>
+      <c r="M11">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="15"/>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12">
         <v>2.1</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I12">
         <v>81</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N12">
+        <v>15</v>
+      </c>
+      <c r="M12">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13">
         <v>2.1</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I13">
         <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>16</v>
-      </c>
-      <c r="N13">
+        <v>15</v>
+      </c>
+      <c r="M13">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14">
         <v>2.1</v>
       </c>
       <c r="H14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I14">
         <v>92</v>
       </c>
       <c r="J14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>16</v>
-      </c>
-      <c r="N14">
+        <v>15</v>
+      </c>
+      <c r="M14">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15">
         <v>2.1</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I15">
         <v>82</v>
       </c>
       <c r="J15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>16</v>
-      </c>
-      <c r="N15">
+        <v>15</v>
+      </c>
+      <c r="M15">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16">
         <v>2.1</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I16">
         <v>79</v>
       </c>
       <c r="J16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>16</v>
-      </c>
-      <c r="N16">
+        <v>15</v>
+      </c>
+      <c r="M16">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17">
         <v>2.1</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I17">
         <v>83</v>
       </c>
       <c r="J17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>16</v>
-      </c>
-      <c r="N17">
+        <v>15</v>
+      </c>
+      <c r="M17">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18">
         <v>2.1</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I18">
         <v>62</v>
       </c>
       <c r="J18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>16</v>
-      </c>
-      <c r="N18">
+        <v>15</v>
+      </c>
+      <c r="M18">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19">
         <v>2.1</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I19">
         <v>71</v>
       </c>
       <c r="J19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>16</v>
-      </c>
-      <c r="N19">
+        <v>15</v>
+      </c>
+      <c r="M19">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" s="15"/>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20">
         <v>2.1</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I20">
         <v>75</v>
       </c>
       <c r="J20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>16</v>
-      </c>
-      <c r="N20">
+        <v>15</v>
+      </c>
+      <c r="M20">
         <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21">
         <v>2.1</v>
       </c>
       <c r="H21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I21">
         <v>77</v>
       </c>
       <c r="J21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>16</v>
-      </c>
-      <c r="N21">
+        <v>15</v>
+      </c>
+      <c r="M21">
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" s="15"/>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22">
         <v>2.1</v>
       </c>
       <c r="H22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I22">
         <v>70</v>
       </c>
       <c r="J22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23">
+        <v>2.1</v>
+      </c>
+      <c r="H23" t="s">
         <v>40</v>
-      </c>
-      <c r="E23">
-        <v>2.1</v>
-      </c>
-      <c r="H23" t="s">
-        <v>41</v>
       </c>
       <c r="I23">
         <v>77</v>
       </c>
       <c r="J23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>16</v>
-      </c>
-      <c r="N23">
+        <v>15</v>
+      </c>
+      <c r="M23">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" s="15"/>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24">
+        <v>2.1</v>
+      </c>
+      <c r="H24" t="s">
         <v>40</v>
-      </c>
-      <c r="E24">
-        <v>2.1</v>
-      </c>
-      <c r="H24" t="s">
-        <v>41</v>
       </c>
       <c r="I24">
         <v>11.2</v>
       </c>
       <c r="J24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K24">
         <v>58.8</v>
       </c>
       <c r="L24" t="s">
-        <v>16</v>
-      </c>
-      <c r="N24">
+        <v>15</v>
+      </c>
+      <c r="M24">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25">
+        <v>2.1</v>
+      </c>
+      <c r="H25" t="s">
         <v>40</v>
-      </c>
-      <c r="E25">
-        <v>2.1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>41</v>
       </c>
       <c r="I25">
         <v>62</v>
       </c>
       <c r="J25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>16</v>
-      </c>
-      <c r="N25">
+        <v>15</v>
+      </c>
+      <c r="M25">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" s="15"/>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26">
+        <v>2.1</v>
+      </c>
+      <c r="H26" t="s">
         <v>40</v>
-      </c>
-      <c r="E26">
-        <v>2.1</v>
-      </c>
-      <c r="H26" t="s">
-        <v>41</v>
       </c>
       <c r="I26">
         <v>14.06</v>
       </c>
       <c r="J26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K26">
         <v>59.94</v>
       </c>
       <c r="L26" t="s">
-        <v>16</v>
-      </c>
-      <c r="N26">
+        <v>15</v>
+      </c>
+      <c r="M26">
         <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27">
+        <v>2.1</v>
+      </c>
+      <c r="H27" t="s">
         <v>40</v>
-      </c>
-      <c r="E27">
-        <v>2.1</v>
-      </c>
-      <c r="H27" t="s">
-        <v>41</v>
       </c>
       <c r="I27">
         <v>38.35</v>
       </c>
       <c r="J27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K27">
         <v>20.65</v>
       </c>
       <c r="L27" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" s="6"/>
-      <c r="N27">
+        <v>15</v>
+      </c>
+      <c r="M27">
         <v>16</v>
       </c>
       <c r="O27" s="6"/>
@@ -1539,34 +1531,33 @@
     <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28">
+        <v>2.1</v>
+      </c>
+      <c r="H28" t="s">
         <v>40</v>
-      </c>
-      <c r="E28">
-        <v>2.1</v>
-      </c>
-      <c r="H28" t="s">
-        <v>41</v>
       </c>
       <c r="I28">
         <v>14.96</v>
       </c>
       <c r="J28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K28">
         <v>53.04</v>
       </c>
       <c r="L28" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" s="6"/>
-      <c r="N28">
+        <v>15</v>
+      </c>
+      <c r="M28">
         <v>16</v>
       </c>
       <c r="O28" s="6"/>
@@ -1576,34 +1567,33 @@
     <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29">
+        <v>2.1</v>
+      </c>
+      <c r="H29" t="s">
         <v>40</v>
-      </c>
-      <c r="E29">
-        <v>2.1</v>
-      </c>
-      <c r="H29" t="s">
-        <v>41</v>
       </c>
       <c r="I29">
         <v>27.5</v>
       </c>
       <c r="J29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K29">
         <v>22.5</v>
       </c>
       <c r="L29" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="6"/>
-      <c r="N29">
+        <v>15</v>
+      </c>
+      <c r="M29">
         <v>16</v>
       </c>
       <c r="O29" s="6"/>
@@ -1613,34 +1603,33 @@
     <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30">
+        <v>2.1</v>
+      </c>
+      <c r="H30" t="s">
         <v>40</v>
-      </c>
-      <c r="E30">
-        <v>2.1</v>
-      </c>
-      <c r="H30" t="s">
-        <v>41</v>
       </c>
       <c r="I30">
         <v>14.25</v>
       </c>
       <c r="J30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K30">
         <v>60.75</v>
       </c>
       <c r="L30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="6"/>
-      <c r="N30">
+        <v>15</v>
+      </c>
+      <c r="M30">
         <v>16.7</v>
       </c>
       <c r="O30" s="6"/>
@@ -1650,34 +1639,33 @@
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
       <c r="D31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31">
+        <v>2.1</v>
+      </c>
+      <c r="H31" t="s">
         <v>40</v>
-      </c>
-      <c r="E31">
-        <v>2.1</v>
-      </c>
-      <c r="H31" t="s">
-        <v>41</v>
       </c>
       <c r="I31">
         <v>50.05</v>
       </c>
       <c r="J31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K31">
         <v>26.95</v>
       </c>
       <c r="L31" t="s">
-        <v>16</v>
-      </c>
-      <c r="M31" s="6"/>
-      <c r="N31">
+        <v>15</v>
+      </c>
+      <c r="M31">
         <v>16.7</v>
       </c>
       <c r="O31" s="6"/>
@@ -1687,34 +1675,33 @@
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" s="15"/>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E32">
         <v>2.1</v>
       </c>
       <c r="H32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I32">
         <v>16.72</v>
       </c>
       <c r="J32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K32">
         <v>59.28</v>
       </c>
       <c r="L32" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" s="6"/>
-      <c r="N32">
+        <v>15</v>
+      </c>
+      <c r="M32">
         <v>16.7</v>
       </c>
       <c r="O32" s="6"/>
@@ -1724,34 +1711,33 @@
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A33" s="15"/>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33">
         <v>2.1</v>
       </c>
       <c r="H33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I33">
         <v>49</v>
       </c>
       <c r="J33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K33">
         <v>21</v>
       </c>
       <c r="L33" t="s">
-        <v>16</v>
-      </c>
-      <c r="M33" s="6"/>
-      <c r="N33">
+        <v>15</v>
+      </c>
+      <c r="M33">
         <v>16.7</v>
       </c>
       <c r="O33" s="6"/>
@@ -1761,34 +1747,33 @@
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A34" s="15"/>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34">
         <v>2.1</v>
       </c>
       <c r="H34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I34">
         <v>5.7</v>
       </c>
       <c r="J34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K34">
         <v>51.3</v>
       </c>
       <c r="L34" t="s">
-        <v>16</v>
-      </c>
-      <c r="M34" s="6"/>
-      <c r="N34">
+        <v>15</v>
+      </c>
+      <c r="M34">
         <v>16.7</v>
       </c>
       <c r="O34" s="6"/>
@@ -1798,34 +1783,33 @@
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A35" s="15"/>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E35">
         <v>2.1</v>
       </c>
       <c r="H35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I35">
         <v>40.799999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K35">
         <v>19.2</v>
       </c>
       <c r="L35" t="s">
-        <v>16</v>
-      </c>
-      <c r="M35" s="6"/>
-      <c r="N35">
+        <v>15</v>
+      </c>
+      <c r="M35">
         <v>16.7</v>
       </c>
       <c r="O35" s="6"/>
@@ -1835,34 +1819,33 @@
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A36" s="15"/>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E36">
         <v>2.1</v>
       </c>
       <c r="H36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I36">
         <v>16.100000000000001</v>
       </c>
       <c r="J36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K36">
         <v>53.9</v>
       </c>
       <c r="L36" t="s">
-        <v>16</v>
-      </c>
-      <c r="M36" s="6"/>
-      <c r="N36">
+        <v>15</v>
+      </c>
+      <c r="M36">
         <v>16.7</v>
       </c>
       <c r="O36" s="6"/>
@@ -1872,34 +1855,33 @@
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A37" s="15"/>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37">
         <v>2.1</v>
       </c>
       <c r="H37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I37">
         <v>33</v>
       </c>
       <c r="J37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K37">
         <v>16.5</v>
       </c>
       <c r="L37" t="s">
-        <v>16</v>
-      </c>
-      <c r="M37" s="6"/>
-      <c r="N37">
+        <v>15</v>
+      </c>
+      <c r="M37">
         <v>16.7</v>
       </c>
       <c r="O37" s="6"/>
@@ -1909,34 +1891,33 @@
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" s="15"/>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38">
         <v>2.1</v>
       </c>
       <c r="H38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I38">
         <v>14.44</v>
       </c>
       <c r="J38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K38">
         <v>61.56</v>
       </c>
       <c r="L38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M38" s="6"/>
-      <c r="N38">
+        <v>15</v>
+      </c>
+      <c r="M38">
         <v>16.7</v>
       </c>
       <c r="O38" s="6"/>
@@ -1946,34 +1927,33 @@
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" s="15"/>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39">
         <v>2.1</v>
       </c>
       <c r="H39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I39">
         <v>42.78</v>
       </c>
       <c r="J39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K39">
         <v>19.22</v>
       </c>
       <c r="L39" t="s">
-        <v>16</v>
-      </c>
-      <c r="M39" s="6"/>
-      <c r="N39">
+        <v>15</v>
+      </c>
+      <c r="M39">
         <v>16.7</v>
       </c>
       <c r="O39" s="6"/>
@@ -1983,34 +1963,33 @@
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" s="15"/>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E40">
         <v>2.1</v>
       </c>
       <c r="H40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I40">
         <v>12.2</v>
       </c>
       <c r="J40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K40">
         <v>48.8</v>
       </c>
       <c r="L40" t="s">
-        <v>16</v>
-      </c>
-      <c r="M40" s="6"/>
-      <c r="N40">
+        <v>15</v>
+      </c>
+      <c r="M40">
         <v>16.7</v>
       </c>
       <c r="O40" s="6"/>
@@ -2020,34 +1999,33 @@
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" s="15"/>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E41">
         <v>2.1</v>
       </c>
       <c r="H41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I41">
         <v>38.35</v>
       </c>
       <c r="J41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K41">
         <v>20.65</v>
       </c>
       <c r="L41" t="s">
-        <v>16</v>
-      </c>
-      <c r="M41" s="6"/>
-      <c r="N41">
+        <v>15</v>
+      </c>
+      <c r="M41">
         <v>16.7</v>
       </c>
       <c r="O41" s="6"/>
@@ -2057,34 +2035,33 @@
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A42" s="15"/>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E42">
         <v>2.1</v>
       </c>
       <c r="H42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I42">
         <v>8.8800000000000008</v>
       </c>
       <c r="J42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K42">
         <v>65.12</v>
       </c>
       <c r="L42" t="s">
-        <v>16</v>
-      </c>
-      <c r="M42" s="6"/>
-      <c r="N42">
+        <v>15</v>
+      </c>
+      <c r="M42">
         <v>16.7</v>
       </c>
       <c r="O42" s="6"/>
@@ -2094,34 +2071,33 @@
     <row r="43" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A43" s="15"/>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E43">
         <v>2.1</v>
       </c>
       <c r="H43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I43">
         <v>56.8</v>
       </c>
       <c r="J43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K43">
         <v>14.2</v>
       </c>
       <c r="L43" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" s="6"/>
-      <c r="N43">
+        <v>15</v>
+      </c>
+      <c r="M43">
         <v>16.7</v>
       </c>
       <c r="O43" s="6"/>
@@ -2131,34 +2107,33 @@
     <row r="44" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A44" s="15"/>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E44">
         <v>2.1</v>
       </c>
       <c r="H44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I44">
         <v>10.199999999999999</v>
       </c>
       <c r="J44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K44">
         <v>49.8</v>
       </c>
       <c r="L44" t="s">
-        <v>16</v>
-      </c>
-      <c r="M44" s="6"/>
-      <c r="N44">
+        <v>15</v>
+      </c>
+      <c r="M44">
         <v>16.7</v>
       </c>
       <c r="O44" s="6"/>
@@ -2168,34 +2143,33 @@
     <row r="45" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A45" s="15"/>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E45">
         <v>2.1</v>
       </c>
       <c r="H45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I45">
         <v>42.78</v>
       </c>
       <c r="J45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K45">
         <v>19.22</v>
       </c>
       <c r="L45" t="s">
-        <v>16</v>
-      </c>
-      <c r="M45" s="6"/>
-      <c r="N45">
+        <v>15</v>
+      </c>
+      <c r="M45">
         <v>16.7</v>
       </c>
       <c r="O45" s="6"/>
@@ -2205,34 +2179,33 @@
     <row r="46" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A46" s="15"/>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E46">
         <v>2.1</v>
       </c>
       <c r="H46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I46">
         <v>12.32</v>
       </c>
       <c r="J46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K46">
         <v>64.680000000000007</v>
       </c>
       <c r="L46" t="s">
-        <v>16</v>
-      </c>
-      <c r="M46" s="6"/>
-      <c r="N46">
+        <v>15</v>
+      </c>
+      <c r="M46">
         <v>16.7</v>
       </c>
       <c r="O46" s="6"/>
@@ -2242,34 +2215,33 @@
     <row r="47" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A47" s="15"/>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C47">
         <v>2</v>
       </c>
       <c r="D47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E47">
         <v>2.1</v>
       </c>
       <c r="H47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I47">
         <v>51</v>
       </c>
       <c r="J47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K47">
         <v>17</v>
       </c>
       <c r="L47" t="s">
-        <v>16</v>
-      </c>
-      <c r="M47" s="6"/>
-      <c r="N47">
+        <v>15</v>
+      </c>
+      <c r="M47">
         <v>16.7</v>
       </c>
       <c r="O47" s="6"/>
@@ -2279,31 +2251,31 @@
     <row r="48" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A48" s="15"/>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C48">
         <v>2</v>
       </c>
       <c r="D48" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48">
+        <v>2.1</v>
+      </c>
+      <c r="H48" t="s">
         <v>40</v>
-      </c>
-      <c r="E48">
-        <v>2.1</v>
-      </c>
-      <c r="H48" t="s">
-        <v>41</v>
       </c>
       <c r="I48">
         <v>16.5</v>
       </c>
       <c r="J48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K48">
         <v>58.5</v>
       </c>
       <c r="L48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M48" s="6"/>
       <c r="N48" s="5"/>
@@ -2314,37 +2286,37 @@
     <row r="49" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A49" s="15"/>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E49">
         <v>2.1</v>
       </c>
       <c r="F49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G49">
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I49">
         <v>51.1</v>
       </c>
       <c r="J49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K49">
         <v>18.899999999999999</v>
       </c>
       <c r="L49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M49" s="6"/>
       <c r="N49" s="5"/>
@@ -2355,37 +2327,37 @@
     <row r="50" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A50" s="15"/>
       <c r="B50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C50">
         <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E50">
         <v>2.1</v>
       </c>
       <c r="F50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I50">
         <v>20.7</v>
       </c>
       <c r="J50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K50">
         <v>25.3</v>
       </c>
       <c r="L50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M50" s="6"/>
       <c r="N50" s="5"/>
@@ -2396,37 +2368,37 @@
     <row r="51" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A51" s="15"/>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C51">
         <v>2</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E51">
         <v>2.1</v>
       </c>
       <c r="F51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I51">
         <v>8.1999999999999993</v>
       </c>
       <c r="J51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K51">
         <v>73.8</v>
       </c>
       <c r="L51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M51" s="6"/>
       <c r="N51" s="5"/>
@@ -2437,37 +2409,37 @@
     <row r="52" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A52" s="15"/>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E52">
         <v>2.1</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I52">
         <v>4.5</v>
       </c>
       <c r="J52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K52">
         <v>85.5</v>
       </c>
       <c r="L52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M52" s="6"/>
       <c r="N52" s="5"/>
@@ -2478,37 +2450,37 @@
     <row r="53" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A53" s="15"/>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C53">
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53">
         <v>2.1</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I53">
         <v>96</v>
       </c>
       <c r="J53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K53">
         <v>0</v>
       </c>
       <c r="L53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M53" s="6"/>
       <c r="N53" s="5"/>
@@ -2519,37 +2491,37 @@
     <row r="54" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A54" s="15"/>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E54">
         <v>2.1</v>
       </c>
       <c r="F54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I54">
         <v>46.8</v>
       </c>
       <c r="J54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K54">
         <v>18.2</v>
       </c>
       <c r="L54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M54" s="6"/>
       <c r="N54" s="5"/>
@@ -2560,37 +2532,37 @@
     <row r="55" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A55" s="15"/>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C55">
         <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E55">
         <v>2.1</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G55">
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I55">
         <v>80</v>
       </c>
       <c r="J55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K55">
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M55" s="6"/>
       <c r="N55" s="5"/>
@@ -2601,37 +2573,37 @@
     <row r="56" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A56" s="15"/>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C56">
         <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E56">
         <v>2.1</v>
       </c>
       <c r="F56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I56">
         <v>51.75</v>
       </c>
       <c r="J56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K56">
         <v>17.25</v>
       </c>
       <c r="L56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M56" s="6"/>
       <c r="N56" s="5"/>
@@ -2642,37 +2614,37 @@
     <row r="57" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A57" s="15"/>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C57">
         <v>2</v>
       </c>
       <c r="D57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E57">
         <v>2.1</v>
       </c>
       <c r="F57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I57">
         <v>6.16</v>
       </c>
       <c r="J57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K57">
         <v>70.84</v>
       </c>
       <c r="L57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M57" s="6"/>
       <c r="N57" s="5"/>
@@ -2683,37 +2655,37 @@
     <row r="58" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A58" s="15"/>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C58">
         <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E58">
         <v>2.1</v>
       </c>
       <c r="F58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I58">
         <v>3.4</v>
       </c>
       <c r="J58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K58">
         <v>17.600000000000001</v>
       </c>
       <c r="L58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M58" s="6"/>
       <c r="N58" s="5"/>
@@ -2724,37 +2696,37 @@
     <row r="59" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A59" s="15"/>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E59">
         <v>2.1</v>
       </c>
       <c r="F59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I59">
         <v>10.5</v>
       </c>
       <c r="J59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K59">
         <v>59.5</v>
       </c>
       <c r="L59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M59" s="6"/>
       <c r="N59" s="5"/>
@@ -2765,37 +2737,37 @@
     <row r="60" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A60" s="15"/>
       <c r="B60" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60" t="s">
+        <v>39</v>
+      </c>
+      <c r="E60">
+        <v>2.1</v>
+      </c>
+      <c r="F60" t="s">
         <v>34</v>
-      </c>
-      <c r="C60">
-        <v>2</v>
-      </c>
-      <c r="D60" t="s">
-        <v>40</v>
-      </c>
-      <c r="E60">
-        <v>2.1</v>
-      </c>
-      <c r="F60" t="s">
-        <v>35</v>
       </c>
       <c r="G60">
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I60">
         <v>32.24</v>
       </c>
       <c r="J60" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K60">
         <v>19.760000000000002</v>
       </c>
       <c r="L60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M60" s="6"/>
       <c r="N60" s="5"/>
@@ -2806,37 +2778,37 @@
     <row r="61" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A61" s="15"/>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E61">
         <v>2.1</v>
       </c>
       <c r="F61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G61">
         <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I61">
         <v>7</v>
       </c>
       <c r="J61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K61">
         <v>43</v>
       </c>
       <c r="L61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M61" s="8"/>
       <c r="N61" s="7"/>
@@ -2847,352 +2819,352 @@
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E62">
         <v>2.1</v>
       </c>
       <c r="F62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I62">
         <v>38.28</v>
       </c>
       <c r="J62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K62">
         <v>19.72</v>
       </c>
       <c r="L62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C63">
         <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E63">
         <v>2.1</v>
       </c>
       <c r="F63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I63">
         <v>10.07</v>
       </c>
       <c r="J63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K63">
         <v>42.93</v>
       </c>
       <c r="L63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C64">
         <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E64">
         <v>2.1</v>
       </c>
       <c r="F64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I64">
         <v>39</v>
       </c>
       <c r="J64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K64">
         <v>21</v>
       </c>
       <c r="L64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C65">
         <v>2</v>
       </c>
       <c r="D65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E65">
         <v>2.1</v>
       </c>
       <c r="F65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I65">
         <v>10.56</v>
       </c>
       <c r="J65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K65">
         <v>55.44</v>
       </c>
       <c r="L65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C66">
         <v>2</v>
       </c>
       <c r="D66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E66">
         <v>2.1</v>
       </c>
       <c r="F66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I66">
         <v>43.4</v>
       </c>
       <c r="J66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K66">
         <v>18.600000000000001</v>
       </c>
       <c r="L66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C67">
         <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E67">
         <v>2.1</v>
       </c>
       <c r="F67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I67">
         <v>9.35</v>
       </c>
       <c r="J67" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K67">
         <v>75.650000000000006</v>
       </c>
       <c r="L67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C68">
         <v>2</v>
       </c>
       <c r="D68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E68">
         <v>2.1</v>
       </c>
       <c r="F68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G68">
         <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I68">
         <v>38.76</v>
       </c>
       <c r="J68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K68">
         <v>18.239999999999998</v>
       </c>
       <c r="L68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C69">
         <v>2</v>
       </c>
       <c r="D69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E69">
         <v>2.1</v>
       </c>
       <c r="F69" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I69">
         <v>8.06</v>
       </c>
       <c r="J69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K69">
         <v>53.94</v>
       </c>
       <c r="L69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C70">
         <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E70">
         <v>2.1</v>
       </c>
       <c r="F70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I70">
         <v>51.2</v>
       </c>
       <c r="J70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K70">
         <v>12.8</v>
       </c>
       <c r="L70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C71">
         <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E71">
         <v>2.1</v>
       </c>
       <c r="F71" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G71">
         <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I71">
         <v>8</v>
       </c>
       <c r="J71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K71">
         <v>72</v>
       </c>
       <c r="L71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
